--- a/feedback_forms/014_employee_complaint_form--feedback_forms.xlsx
+++ b/feedback_forms/014_employee_complaint_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -690,7 +690,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>resolution_time</t>
+          <t>Resolution Date Time</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>resolution_status</t>
+          <t>resolution_status_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>resolution_status</t>
+          <t>Resolution Status 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -754,12 +754,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>resolution_date</t>
+          <t>resolution_date_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>resolution_date</t>
+          <t>Resolution Date 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -777,12 +777,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>resolution_time</t>
+          <t>resolution_time_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>resolution_time</t>
+          <t>Resolution Time 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -800,12 +800,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>resolution_date_time</t>
+          <t>resolution_date_time_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>resolution_date_time</t>
+          <t>Resolution Date Time 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -823,12 +823,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>resolution_note</t>
+          <t>resolution_note_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>resolution_note</t>
+          <t>Resolution Note 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -875,7 +875,7 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
@@ -951,7 +951,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>resolution_status_choices</t>
+          <t>resolution_status_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -968,7 +968,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>resolution_status_choices</t>
+          <t>resolution_status_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -985,7 +985,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>resolution_status_choices</t>
+          <t>resolution_status_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
